--- a/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/In/cfg_activity_rule.xlsx
+++ b/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/In/cfg_activity_rule.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="164">
   <si>
     <t>编号</t>
   </si>
@@ -427,7 +427,7 @@
     <t>黄金部队</t>
   </si>
   <si>
-    <t xml:space="preserve">0 0 19&amp;20 ? * 6 </t>
+    <t xml:space="preserve">0 0 19 ? * 6 </t>
   </si>
   <si>
     <t>冰风堡攻城战</t>
@@ -515,9 +515,6 @@
   </si>
   <si>
     <t>卡利玛神庙</t>
-  </si>
-  <si>
-    <t>1#5</t>
   </si>
   <si>
     <t>&amp;</t>
@@ -1809,7 +1806,7 @@
       <c r="G2" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="H2" s="6" t="s">
         <v>33</v>
       </c>
       <c r="I2" s="6" t="s">
@@ -2050,7 +2047,7 @@
         <v>1</v>
       </c>
       <c r="J5" s="1">
-        <v>15</v>
+        <v>9999</v>
       </c>
       <c r="K5" s="1">
         <v>1</v>
@@ -2114,7 +2111,7 @@
         <v>1</v>
       </c>
       <c r="J6" s="1">
-        <v>15</v>
+        <v>9999</v>
       </c>
       <c r="K6" s="1">
         <v>1</v>
@@ -2713,10 +2710,10 @@
         <v>60</v>
       </c>
       <c r="F16" s="5">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G16" s="10" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="H16" s="5" t="s">
         <v>88</v>
@@ -2771,7 +2768,7 @@
         <v>0</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J15" s="1">
         <v>0</v>
@@ -2785,16 +2782,16 @@
         <v>10</v>
       </c>
       <c r="I16" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="J16" s="1" t="s">
         <v>153</v>
-      </c>
-      <c r="J16" s="1" t="s">
-        <v>154</v>
       </c>
       <c r="K16" s="1">
         <v>14</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="M16" s="1">
         <v>14</v>
@@ -2805,19 +2802,19 @@
         <v>20</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="K17" s="1">
         <v>15</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="M17" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="18" ht="16.5" spans="8:13">
@@ -2825,19 +2822,19 @@
         <v>30</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="K18" s="1">
         <v>16</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="M18" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="19" ht="16.5" spans="8:13">
@@ -2845,19 +2842,19 @@
         <v>40</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="K19" s="1">
         <v>17</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="M19" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="20" ht="16.5" spans="8:13">
@@ -2865,19 +2862,19 @@
         <v>50</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="K20" s="1">
         <v>18</v>
       </c>
       <c r="L20" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="M20" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="21" ht="16.5" spans="8:13">
@@ -2885,29 +2882,29 @@
         <v>19</v>
       </c>
       <c r="L21" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="M21" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="22" ht="16.5" spans="8:13">
       <c r="J22" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="K22" s="1">
         <v>20</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="M22" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="23" ht="16.5" spans="8:13">
       <c r="J23" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
   </sheetData>
